--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a1.00_b1.00_x0.30_Q40_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a1.00_b1.00_x0.30_Q40_LO.xlsx
@@ -455,10 +455,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03176481968937318</v>
+        <v>0.01624252021065276</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03176481968937318</v>
+        <v>0.01624252021065276</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.03106941537686736</v>
+        <v>0.01587206290694231</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03106941537686736</v>
+        <v>0.01587206290694231</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -483,10 +483,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03563782845040479</v>
+        <v>0.01839953706792383</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03563782845040479</v>
+        <v>0.01839953706792383</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -497,10 +497,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.04946664133216415</v>
+        <v>0.02583320264277435</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04946664133216415</v>
+        <v>0.02583320264277435</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -511,10 +511,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.07070324320450183</v>
+        <v>0.03703638479166549</v>
       </c>
       <c r="C6" t="n">
-        <v>0.07070324320450183</v>
+        <v>0.03703638479166549</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -525,10 +525,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.09366154195364249</v>
+        <v>0.04888392423407425</v>
       </c>
       <c r="C7" t="n">
-        <v>0.09366154195364249</v>
+        <v>0.04888392423407425</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -539,10 +539,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1206949724889363</v>
+        <v>0.06284145305238101</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1206949724889363</v>
+        <v>0.06284145305238101</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -553,10 +553,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1518585839419535</v>
+        <v>0.07913739234228445</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1518585839419535</v>
+        <v>0.07913739234228445</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -567,10 +567,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1793389588281024</v>
+        <v>0.09360889595816568</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1793389588281024</v>
+        <v>0.09360889595816568</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -581,10 +581,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1992010541093994</v>
+        <v>0.104035301062451</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1992010541093994</v>
+        <v>0.104035301062451</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -595,10 +595,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.2094763561877679</v>
+        <v>0.1093768203896454</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2094763561877679</v>
+        <v>0.1093768203896454</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -609,10 +609,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2139093025011164</v>
+        <v>0.1116296856085256</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2139093025011164</v>
+        <v>0.1116296856085256</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -623,10 +623,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.2115413828051957</v>
+        <v>0.1103569380144496</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2115413828051957</v>
+        <v>0.1103569380144496</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -637,10 +637,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.2071992398372803</v>
+        <v>0.1080959838854027</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2071992398372803</v>
+        <v>0.1080959838854027</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -651,10 +651,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.1977932672770478</v>
+        <v>0.1031860532306322</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1977932672770478</v>
+        <v>0.1031860532306322</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -665,10 +665,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.1942224147264756</v>
+        <v>0.1012976641982213</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1942224147264756</v>
+        <v>0.1012976641982213</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -679,10 +679,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.1859926819114664</v>
+        <v>0.09712394057353727</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1859926819114664</v>
+        <v>0.09712394057353727</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.1812758637597491</v>
+        <v>0.09463665216141479</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1812758637597491</v>
+        <v>0.09463665216141479</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -707,10 +707,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.1779405661024187</v>
+        <v>0.09299309177683314</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1779405661024187</v>
+        <v>0.09299309177683314</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -721,10 +721,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.1748239108857489</v>
+        <v>0.09134977509889035</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1748239108857489</v>
+        <v>0.09134977509889035</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
